--- a/food_statistics.xlsx
+++ b/food_statistics.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -463,7 +463,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>佛山</t>
+          <t>中山</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -493,11 +493,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>重样</t>
+          <t>在家</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -508,11 +508,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>做饭</t>
+          <t>午餐</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -523,7 +523,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>一人食</t>
+          <t>做饭</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -538,11 +538,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>灵感</t>
+          <t>晚饭</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -553,11 +553,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>一周</t>
+          <t>夏天</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -568,11 +568,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>提供</t>
+          <t>幸福</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -583,11 +583,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>吃饭</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>电锅</t>
+          <t>馆子</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -613,7 +613,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>得到</t>
+          <t>点名</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -628,7 +628,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>攻略</t>
+          <t>苍蝇</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -643,7 +643,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>人生</t>
+          <t>这家</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -658,7 +658,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>离开</t>
+          <t>阿炮</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -673,7 +673,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>建议</t>
+          <t>美食城</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -688,7 +688,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>同华路</t>
+          <t>一定</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -703,7 +703,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>必吃</t>
+          <t>同华路</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -718,7 +718,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>食记</t>
+          <t>必吃</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -733,7 +733,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>一人</t>
+          <t>佛山</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -748,7 +748,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>哪家</t>
+          <t>大转盘</t>
         </is>
       </c>
       <c r="B22" t="n">

--- a/food_statistics.xlsx
+++ b/food_statistics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -463,22 +463,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>中山</t>
+          <t>披萨</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>keywords</t>
+          <t>food_distribution</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>合集</t>
+          <t>佛山</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -493,11 +493,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>在家</t>
+          <t>家常菜</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -508,7 +508,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>午餐</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -523,7 +523,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>做饭</t>
+          <t>做法</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -538,11 +538,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>晚饭</t>
+          <t>最近</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -553,7 +553,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>夏天</t>
+          <t>必看</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -568,7 +568,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>幸福</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -583,7 +583,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>吃饭</t>
+          <t>新手</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -598,7 +598,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>馆子</t>
+          <t>炒菜</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -613,7 +613,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>点名</t>
+          <t>应季</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -628,7 +628,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>苍蝇</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -643,7 +643,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>这家</t>
+          <t>控糖</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -658,7 +658,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>阿炮</t>
+          <t>升糖慢</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -673,7 +673,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>美食城</t>
+          <t>家常</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -688,7 +688,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>一定</t>
+          <t>披萨</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -703,7 +703,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>同华路</t>
+          <t>一些</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -718,7 +718,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>必吃</t>
+          <t>禅城</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -733,7 +733,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>佛山</t>
+          <t>citywalk</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -748,13 +748,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>大转盘</t>
+          <t>国庆</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="inlineStr">
+        <is>
+          <t>keywords</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>祖庙</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>keywords</t>
         </is>

--- a/food_statistics.xlsx
+++ b/food_statistics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -463,26 +463,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>披萨</t>
+          <t>家常菜</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>food_distribution</t>
+          <t>keywords</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>佛山</t>
+          <t>做饭</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -493,7 +493,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>家常菜</t>
+          <t>成本</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -508,7 +508,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>简单</t>
+          <t>适合</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -523,7 +523,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>做法</t>
+          <t>合集</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -538,7 +538,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>最近</t>
+          <t>独居</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -553,11 +553,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>必看</t>
+          <t>阿姨</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -568,11 +568,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>挑战</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -583,11 +583,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>新手</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -598,11 +598,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>炒菜</t>
+          <t>做法</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>应季</t>
+          <t>九款</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -628,7 +628,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>新手</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -643,7 +643,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>控糖</t>
+          <t>成本低</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -658,7 +658,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>升糖慢</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -673,7 +673,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>家常</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -688,7 +688,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>披萨</t>
+          <t>年夜饭</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -703,7 +703,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>一些</t>
+          <t>团圆</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -718,7 +718,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>禅城</t>
+          <t>备战</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -733,7 +733,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>citywalk</t>
+          <t>佛山</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -748,28 +748,13 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>国庆</t>
+          <t>叔叔</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="inlineStr">
-        <is>
-          <t>keywords</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>祖庙</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" t="inlineStr">
         <is>
           <t>keywords</t>
         </is>
